--- a/mapping_surveyor.xlsx
+++ b/mapping_surveyor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angga\Documents\Angga Reinaldi\2026\Python\Sildenafil Package\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C50CB1-DFFC-43AC-8F3A-60A9A671FC60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F61D22E-5BC9-48A1-AAF7-61D66EE29977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="197">
   <si>
     <t>Surveyor ID</t>
   </si>
@@ -619,6 +619,12 @@
   </si>
   <si>
     <t>Vacant - eks Arie Gianjar</t>
+  </si>
+  <si>
+    <t>TSSBDG</t>
+  </si>
+  <si>
+    <t>JKA01</t>
   </si>
 </sst>
 </file>
@@ -2345,6 +2351,9 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>195</v>
+      </c>
       <c r="B82" t="s">
         <v>193</v>
       </c>
@@ -2359,6 +2368,9 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>196</v>
+      </c>
       <c r="B83" t="s">
         <v>194</v>
       </c>
